--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -4810,7 +4810,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -4810,7 +4810,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -4810,7 +4810,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -4810,7 +4810,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -4810,7 +4810,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -4810,7 +4810,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -4810,7 +4810,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -4810,7 +4810,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -4810,7 +4810,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -4810,7 +4810,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -4810,7 +4810,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -4810,7 +4810,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -4810,7 +4810,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -4810,7 +4810,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -4810,7 +4810,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260407_203819.xlsx
@@ -4810,7 +4810,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
